--- a/analysis/myclass-chatbot/data/202606_마이클래스-챗봇_로우데이터.xlsx
+++ b/analysis/myclass-chatbot/data/202606_마이클래스-챗봇_로우데이터.xlsx
@@ -25,6 +25,7 @@
     <sheet name="카카오_발신비율" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="카카오_단계별대체" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="카카오_전수분류" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="카카오_신뢰구간" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +51,19 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -75,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -83,11 +97,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E0D5C0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E0D5C0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0D5C0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0D5C0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -100,6 +128,17 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -848,6 +887,26 @@
       </c>
       <c r="D20" t="n">
         <v>116</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>카카오_신뢰구간</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Wilson 95% CI(n=162)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1032,11 +1091,9 @@
       <c r="C3" t="n">
         <v>26.1</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>59.6</v>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1050,11 +1107,9 @@
       <c r="C4" t="n">
         <v>69.3</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6854,6 +6909,266 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="008A5A00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>대화수</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>점추정%</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Wilson95_하한%</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Wilson95_상한%</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>반폭%p</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>표본</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>조회(1차 챗봇)</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>n=162</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>처리(2차 기능)</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>n=162</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>계정·번호 꼬임</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>n=162</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>사람 상담</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>n=162</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>노이즈</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>n=162</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1차 누적(조회+계정)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>n=162</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>2차 누적(+처리)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>129</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>n=162</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>주: 카카오 census는 n=162 표본 → 모든 비율은 Wilson 95% 신뢰구간(±5~7%p)을 동반. AMS 81,863건은 운영DB 전수라 표본오차 없음(점추정 그대로 사용).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
